--- a/02_Tier/02_WorkProduct/doc/engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-002_SW 통합시험 케이스.xlsx
+++ b/02_Tier/02_WorkProduct/doc/engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-002_SW 통합시험 케이스.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -900,6 +900,191 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IT-P2-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CrashReleasePolicy+InputGateway</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>crash_status=CONFIRMED, 접근위험=False</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>요구사항기반시험</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IT-P2-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SWR-005</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ApproachRiskPolicy+InputGateway</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>접근위험=True, 크래시 없음</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LOCK</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>요구사항기반시험</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IT-P2-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SWR-007, SWR-005</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CrashReleasePolicy+ApproachRiskPolicy</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>crash_status=CONFIRMED, 접근위험=True 동시 발생</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RELEASE (P1&gt;P3 우선순위)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>요구사항기반시험, 의사결정표기반</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IT-P2-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SWR-021, SWR-007, SWR-005</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SensorFaultGate+CrashReleasePolicy+ApproachRiskPolicy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sensor_fault=True, crash_status=CONFIRMED, 접근위험=True</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HOLD_LAST_OUTPUT (P0 게이트 최우선)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>결함주입시험</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IT-P2-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SWR-013, SWR-007</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DegradedStateManager+CrashReleasePolicy</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>staleness=0.3s, crash_status=CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DEGRADED=True 이면서 RELEASE (모듈 독립성)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>요구사항기반시험</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>자동(unittest)</t>
         </is>

--- a/02_Tier/02_WorkProduct/doc/engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-002_SW 통합시험 케이스.xlsx
+++ b/02_Tier/02_WorkProduct/doc/engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-002_SW 통합시험 케이스.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1085,6 +1085,228 @@
         </is>
       </c>
       <c r="G18" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IT-P3-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ForcedReleasePolicy+InputGateway</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>fire_detected=True</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>요구사항기반시험</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IT-P3-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SWR-017, SWR-005</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ForcedReleasePolicy+ApproachRiskPolicy</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>화재=True, 접근위험=True 동시</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RELEASE (P2&gt;P3)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>의사결정표기반</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IT-P3-03</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SWR-018, SWR-020</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IsofixLockPolicy+IgnitionOffPolicy</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>isofix_left=True, ignition_on=False 동시</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LOCK (P4&gt;P5)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>의사결정표기반</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IT-P3-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SWR-007, SWR-017</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CrashReleasePolicy+ForcedReleasePolicy</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>crash_status=CONFIRMED, fire_detected=True 동시</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RELEASE (동일결과 일관성)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>요구사항기반시험</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IT-P3-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SWR-021, SWR-017, SWR-018</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SensorFaultGate+ForcedReleasePolicy+IsofixLockPolicy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sensor_fault=True, fire_detected=True, isofix_left=True</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HOLD_LAST_OUTPUT (P0 최우선)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>결함주입시험</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>자동(unittest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IT-P3-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Phase1~3 전체 정책</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>모든 트리거 False</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vote 없음</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>요구사항기반시험</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>자동(unittest)</t>
         </is>
